--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-consent.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-consent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-consent.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-consent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-consent.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-consent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-consent.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-consent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -272,7 +272,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}ppc-1:ポリシーまたはPolicyruleのいずれか / Either a Policy or PolicyRule {policy.exists() or policyRule.exists()}ppc-2:scope =プライバシーの場合、患者がいる必要があります / IF Scope=privacy, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='patient-privacy').exists().not()}ppc-3:scope =研究の場合、患者がいる必要があります / IF Scope=research, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='research').exists().not()}ppc-4:scope = adrの場合、患者がいる必要があります / IF Scope=adr, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='adr').exists().not()}ppc-5:scope =治療の場合、患者がいる必要があります / IF Scope=treatment, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='treatment').exists().not()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}ppc-1:ポリシーまたはPolicyruleのいずれか / Either a Policy or PolicyRule {policy.exists() or policyRule.exists()}ppc-2:scope =プライバシーの場合、患者がいる必要があります / IF Scope=privacy, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='patient-privacy').exists().not()}ppc-3:scope =研究の場合、患者がいる必要があります / IF Scope=research, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='research').exists().not()}ppc-4:scope = adrの場合、患者がいる必要があります / IF Scope=adr, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='adr').exists().not()}ppc-5:scope =治療の場合、患者がいる必要があります / IF Scope=treatment, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='treatment').exists().not()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -382,7 +382,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Consent.meta.versionId</t>
@@ -669,7 +669,7 @@
     <t>Consent.status</t>
   </si>
   <si>
-    <t>ドラフト|提案|アクティブ|拒否|非アクティブ|エラーに入った / draft | proposed | active | rejected | inactive | entered-in-error</t>
+    <t>ドラフト | 提案 | アクティブ | 拒否 | 非アクティブ | エラー入力 / draft | proposed | active | rejected | inactive | entered-in-error</t>
   </si>
   <si>
     <t>この同意の現在の状態を示します。 / Indicates the current state of this consent.</t>
@@ -1184,7 +1184,7 @@
     <t>Consent.provision.code</t>
   </si>
   <si>
-    <t>例えばコンテンツ内の泡またはSNOMED-CTコードなど / e.g. LOINC or SNOMED CT code, etc. in the content</t>
+    <t>例えばコンテンツ内のLoincまたはSNOMED-CTコードなど / e.g. LOINC or SNOMED CT code, etc. in the content</t>
   </si>
   <si>
     <t>このコードがインスタンスで見つかった場合、ルールが適用されます。 / If this code is found in an instance, then the rule applies.</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-consent.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-consent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-release</t>
+    <t>1.2.0-b</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-consent.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-consent.xlsx
@@ -1081,13 +1081,13 @@
     <t>Consent.provision.actor.role</t>
   </si>
   <si>
-    <t>俳優がどのように関与しているか / How the actor is involved</t>
+    <t>同意書対象者がどのように関与しているか / How the actor is involved</t>
   </si>
   <si>
     <t>個人が例外で説明されているリソースコンテンツにどのように関与しているか。 / How the individual is involved in the resources content that is described in the exception.</t>
   </si>
   <si>
-    <t>俳優が同意の考慮事項にどのように関与しているか。 / How an actor is involved in the consent considerations.</t>
+    <t>同意書対象者が同意の考慮事項にどのように関与しているか。 / How an actor is involved in the consent considerations.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/security-role-type</t>
@@ -1100,10 +1100,10 @@
 </t>
   </si>
   <si>
-    <t>俳優のためのリソース（またはグループ、役割） / Resource for the actor (or group, by role)</t>
-  </si>
-  <si>
-    <t>俳優を識別するリソース。タイプごとに俳優を特定するには、グループを使用して、共有する一部の財産（「役員を入院する」など）によって一連のアクターを特定します。 / The resource that identifies the actor. To identify actors by type, use group to identify a set of actors by some property they share (e.g. 'admitting officers').</t>
+    <t>同意書対象者のためのリソース（またはグループ、役割） / Resource for the actor (or group, by role)</t>
+  </si>
+  <si>
+    <t>同意書対象者を識別するリソース。タイプごとに同意書対象者を特定するには、グループを使用して、共有する一部の財産（「役員を入院する」など）によって一連のアクターを特定します。 / The resource that identifies the actor. To identify actors by type, use group to identify a set of actors by some property they share (e.g. 'admitting officers').</t>
   </si>
   <si>
     <t>Consent.provision.action</t>
